--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jun-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3934.08</v>
+        <v>3990.37</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>845.37</v>
+        <v>857.47</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5570.93</v>
+        <v>5650.64</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5936.93</v>
+        <v>6021.88</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1333.74</v>
+        <v>1352.82</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4332.3</v>
+        <v>4394.29</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1117.7</v>
+        <v>1133.69</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>940.6900000000001</v>
+        <v>954.15</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>913.52</v>
+        <v>926.6</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10328.94</v>
+        <v>10476.74</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>783.1900000000001</v>
+        <v>794.39</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4139.73</v>
+        <v>4198.97</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2219.47</v>
+        <v>2251.22</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>870.45</v>
+        <v>882.91</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2374.89</v>
+        <v>2408.87</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1469.39</v>
+        <v>1490.41</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21376.99</v>
+        <v>21682.88</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4275.33</v>
+        <v>4336.5</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1386.76</v>
+        <v>1406.6</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1550.12</v>
+        <v>1572.3</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1130.95</v>
+        <v>1147.14</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4098.02</v>
+        <v>4156.66</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1194.95</v>
+        <v>1212.05</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>18732.8</v>
+        <v>19000.85</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>950.77</v>
+        <v>964.37</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>13612.26</v>
+        <v>13771.94</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4252.95</v>
+        <v>4302.84</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>797.08</v>
+        <v>806.4299999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2184.95</v>
+        <v>2210.58</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>829.52</v>
+        <v>839.25</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1021.46</v>
+        <v>1033.44</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1061.52</v>
+        <v>1073.97</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2663.16</v>
+        <v>2694.4</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8006.36</v>
+        <v>8100.28</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4935.95</v>
+        <v>4993.85</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>793.33</v>
+        <v>802.64</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2824.2</v>
+        <v>2857.33</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1668.85</v>
+        <v>1688.42</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3780.06</v>
+        <v>3824.4</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1264.94</v>
+        <v>1279.78</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7495.92</v>
+        <v>7583.85</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2181.16</v>
+        <v>2206.74</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3241.84</v>
+        <v>3279.87</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1007.85</v>
+        <v>1019.68</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8505.68</v>
+        <v>8605.450000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>974.3200000000001</v>
+        <v>985.75</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4849.97</v>
+        <v>4906.87</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1803.47</v>
+        <v>1824.63</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4460.01</v>
+        <v>4512.33</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1506.19</v>
+        <v>1523.86</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4580.07</v>
+        <v>4633.8</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2703.45</v>
+        <v>2735.16</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2805.45</v>
+        <v>2838.36</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5640.8</v>
+        <v>5706.97</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1058.25</v>
+        <v>1070.67</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1692.23</v>
+        <v>1712.09</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2531.17</v>
+        <v>2560.86</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1790.42</v>
+        <v>1811.42</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3176.52</v>
+        <v>3213.78</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>919.27</v>
+        <v>930.05</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2630.95</v>
+        <v>2661.81</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4504.66</v>
+        <v>4557.5</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1323.53</v>
+        <v>1339.05</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>970.67</v>
+        <v>982.0599999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5319.91</v>
+        <v>5409.88</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1932.17</v>
+        <v>1964.85</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1775.65</v>
+        <v>1805.68</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>962.1</v>
+        <v>978.37</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4770.35</v>
+        <v>4851.02</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2113.02</v>
+        <v>2148.75</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2133.19</v>
+        <v>2169.26</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1035.41</v>
+        <v>1052.92</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>945.84</v>
+        <v>961.84</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>957.0599999999999</v>
+        <v>973.24</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>945.35</v>
+        <v>961.34</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2309.04</v>
+        <v>2348.09</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1498.92</v>
+        <v>1524.27</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1632.32</v>
+        <v>1659.93</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3237.78</v>
+        <v>3292.54</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3000.18</v>
+        <v>3050.92</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1297.77</v>
+        <v>1319.72</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>14511.03</v>
+        <v>14756.45</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2742.11</v>
+        <v>2788.48</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3712.42</v>
+        <v>3775.2</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>11720.7</v>
+        <v>11918.93</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6375.58</v>
+        <v>6483.41</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1809.53</v>
+        <v>1840.13</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2313.26</v>
+        <v>2352.39</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1685.19</v>
+        <v>1713.69</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1599.48</v>
+        <v>1626.53</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1191.74</v>
+        <v>1211.89</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2393.61</v>
+        <v>2417.95</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>6654.32</v>
+        <v>6721.99</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2034.59</v>
+        <v>2055.28</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1761.19</v>
+        <v>1779.1</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1132.85</v>
+        <v>1144.37</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>13119.01</v>
+        <v>13252.42</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1131.28</v>
+        <v>1142.79</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1777.65</v>
+        <v>1795.73</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1535.94</v>
+        <v>1551.55</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3272.1</v>
+        <v>3305.37</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2401.72</v>
+        <v>2426.15</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>825.14</v>
+        <v>833.53</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>869.4</v>
+        <v>878.24</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1064.46</v>
+        <v>1075.28</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2287.57</v>
+        <v>2310.83</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1249.8</v>
+        <v>1262.51</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>811.38</v>
+        <v>819.63</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>841.27</v>
+        <v>849.83</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>802.99</v>
+        <v>811.16</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>7969.59</v>
+        <v>8050.64</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>960.83</v>
+        <v>970.6</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>8634.459999999999</v>
+        <v>8722.27</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1195.09</v>
+        <v>1207.24</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2212.05</v>
+        <v>2234.54</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>960.75</v>
+        <v>970.52</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6337.12</v>
+        <v>6401.56</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2216.14</v>
+        <v>2238.67</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1897.79</v>
+        <v>1917.09</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1060.58</v>
+        <v>1071.37</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5334.94</v>
+        <v>5389.19</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>792.26</v>
+        <v>800.3099999999999</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>19326.35</v>
+        <v>19522.88</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1307.65</v>
+        <v>1320.95</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2834.24</v>
+        <v>2863.06</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1098.08</v>
+        <v>1109.24</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1229.97</v>
+        <v>1242.48</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1617.61</v>
+        <v>1634.06</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2595.02</v>
+        <v>2621.41</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1014.57</v>
+        <v>1024.89</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2535.48</v>
+        <v>2561.26</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1468.73</v>
+        <v>1483.66</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>28565.24</v>
+        <v>28833.16</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4394.83</v>
+        <v>4436.05</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1227.54</v>
+        <v>1239.05</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4522.44</v>
+        <v>4564.86</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1769.22</v>
+        <v>1785.82</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>793.6799999999999</v>
+        <v>801.12</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1735.05</v>
+        <v>1751.32</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>940.83</v>
+        <v>949.66</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>791.8099999999999</v>
+        <v>799.24</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3479.01</v>
+        <v>3511.64</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3259.86</v>
+        <v>3290.43</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>42450.6</v>
+        <v>42848.76</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1026.07</v>
+        <v>1035.69</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>14382.6</v>
+        <v>14517.5</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1122.84</v>
+        <v>1133.37</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2588.62</v>
+        <v>2612.9</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3415.48</v>
+        <v>3447.52</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1056.23</v>
+        <v>1066.14</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1565.9</v>
+        <v>1580.59</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5402.59</v>
+        <v>5453.27</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>897.78</v>
+        <v>906.21</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1160.77</v>
+        <v>1171.65</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2618.75</v>
+        <v>2643.31</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>894.8200000000001</v>
+        <v>903.21</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>12402.16</v>
+        <v>12518.48</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3872.94</v>
+        <v>3909.27</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2934.61</v>
+        <v>2962.14</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2041.04</v>
+        <v>2060.19</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1379.32</v>
+        <v>1368.85</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1693.61</v>
+        <v>1680.76</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3965.41</v>
+        <v>3935.33</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>793.04</v>
+        <v>787.02</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2911.16</v>
+        <v>2889.08</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>899.61</v>
+        <v>892.79</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2611.77</v>
+        <v>2591.96</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1899.38</v>
+        <v>1884.97</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>846.84</v>
+        <v>840.41</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1080.88</v>
+        <v>1072.69</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1874.47</v>
+        <v>1860.25</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1126.26</v>
+        <v>1117.72</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>5640.09</v>
+        <v>5597.3</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>887.1799999999999</v>
+        <v>880.45</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>996.5700000000001</v>
+        <v>989.01</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4459.22</v>
+        <v>4425.39</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1832.98</v>
+        <v>1819.07</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>22369.99</v>
+        <v>22200.28</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2742.87</v>
+        <v>2722.06</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>982.8099999999999</v>
+        <v>975.35</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>917.77</v>
+        <v>910.8099999999999</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2111.28</v>
+        <v>2095.26</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>813.53</v>
+        <v>807.36</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1049.79</v>
+        <v>1032.05</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3299.82</v>
+        <v>3244.07</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>4187.33</v>
+        <v>4116.59</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1094.52</v>
+        <v>1076.03</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>798.58</v>
+        <v>785.09</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1584.91</v>
+        <v>1558.13</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3230.07</v>
+        <v>3175.5</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1550.22</v>
+        <v>1524.03</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>5936.56</v>
+        <v>5836.26</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2943.67</v>
+        <v>2893.94</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>970.65</v>
+        <v>954.25</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>869.05</v>
+        <v>854.37</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2378.8</v>
+        <v>2338.61</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1827.18</v>
+        <v>1796.31</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2440.42</v>
+        <v>2399.18</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>888</v>
+        <v>873</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>808.8</v>
+        <v>795.14</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>792.46</v>
+        <v>779.0700000000001</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>826.8</v>
+        <v>812.83</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1396.38</v>
+        <v>1372.79</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>793.83</v>
+        <v>780.42</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>793.6900000000001</v>
+        <v>780.28</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>884.14</v>
+        <v>869.2</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>793.8200000000001</v>
+        <v>780.4</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1311.09</v>
+        <v>1288.94</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1459.57</v>
+        <v>1434.91</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3589.9</v>
+        <v>3529.25</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>20605.47</v>
+        <v>20257.32</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>5896.77</v>
+        <v>5797.14</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1009.36</v>
+        <v>992.3</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>5707.33</v>
+        <v>5610.9</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2039.13</v>
+        <v>2004.68</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1465.59</v>
+        <v>1440.83</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>828.9299999999999</v>
+        <v>814.9299999999999</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>826.41</v>
+        <v>812.45</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>9585.629999999999</v>
+        <v>9423.68</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1032.86</v>
+        <v>1015.41</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>7056.13</v>
+        <v>6936.91</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>791.63</v>
+        <v>778.25</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2073.55</v>
+        <v>2038.52</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1495.1</v>
+        <v>1469.84</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>895.45</v>
+        <v>880.3200000000001</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>870.71</v>
+        <v>858.36</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1112.8</v>
+        <v>1097.01</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1075.04</v>
+        <v>1059.78</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2073.28</v>
+        <v>2043.85</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>958.71</v>
+        <v>945.1</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1584.35</v>
+        <v>1561.86</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>796.49</v>
+        <v>785.1799999999999</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1370.22</v>
+        <v>1350.78</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1401.43</v>
+        <v>1381.54</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2185.22</v>
+        <v>2154.2</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2501.29</v>
+        <v>2465.79</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2627.39</v>
+        <v>2590.11</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>18742.38</v>
+        <v>18476.39</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2650</v>
+        <v>2612.39</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3329.36</v>
+        <v>3282.11</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1661.27</v>
+        <v>1637.69</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>5245.06</v>
+        <v>5170.62</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1881.26</v>
+        <v>1854.56</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1490.23</v>
+        <v>1469.08</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>990.78</v>
+        <v>976.72</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1596.2</v>
+        <v>1573.55</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>892.87</v>
+        <v>880.2</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3776.61</v>
+        <v>3723.01</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2396.51</v>
+        <v>2362.5</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>4362.37</v>
+        <v>4300.46</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1839.57</v>
+        <v>1813.46</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>794.98</v>
+        <v>783.7</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1099.5</v>
+        <v>1083.89</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1730.27</v>
+        <v>1705.72</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2524.35</v>
+        <v>2489.66</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3066.21</v>
+        <v>3024.08</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>841.95</v>
+        <v>830.38</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>992.29</v>
+        <v>978.65</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1947</v>
+        <v>1920.25</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1312</v>
+        <v>1293.97</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2666.32</v>
+        <v>2629.69</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>792.85</v>
+        <v>781.95</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2239.01</v>
+        <v>2208.24</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1955.88</v>
+        <v>1929.01</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>3240.48</v>
+        <v>3195.96</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>30502.04</v>
+        <v>30082.93</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2888.49</v>
+        <v>2848.81</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>3117.88</v>
+        <v>3075.04</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2588.67</v>
+        <v>2553.1</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4120.42</v>
+        <v>4063.8</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>945.54</v>
+        <v>932.54</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>6369.32</v>
+        <v>6281.81</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1326.71</v>
+        <v>1308.49</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>959.89</v>
+        <v>946.7</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1937.7</v>
+        <v>1911.08</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>5236.37</v>
+        <v>5164.42</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>873.98</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>3692.99</v>
+        <v>3642.25</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>6078.14</v>
+        <v>5994.63</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>4407.54</v>
+        <v>4346.97</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2078.47</v>
+        <v>2049.91</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1366.01</v>
+        <v>1347.24</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1588.9</v>
+        <v>1567.06</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>3509.59</v>
+        <v>3461.37</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2349.13</v>
+        <v>2316.85</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1602.53</v>
+        <v>1580.51</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>7835.08</v>
+        <v>7727.42</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1104.49</v>
+        <v>1089.31</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>11069.07</v>
+        <v>10916.98</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>995.26</v>
+        <v>981.59</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3230.47</v>
+        <v>3186.08</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1158.97</v>
+        <v>1143.04</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1109.08</v>
+        <v>1093.84</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1499.05</v>
+        <v>1478.45</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>926.9</v>
+        <v>914.16</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>977.4400000000001</v>
+        <v>971.38</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1101.76</v>
+        <v>1094.93</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>6802.18</v>
+        <v>6760.01</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1930.95</v>
+        <v>1918.98</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>10230.34</v>
+        <v>10166.92</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4101.52</v>
+        <v>4076.09</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>4928.59</v>
+        <v>4898.03</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>13691.34</v>
+        <v>13606.46</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>874.35</v>
+        <v>868.9299999999999</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1659.9</v>
+        <v>1649.6</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2261.04</v>
+        <v>2247.02</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>6388.26</v>
+        <v>6348.66</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2213.77</v>
+        <v>2200.05</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1344.22</v>
+        <v>1335.89</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2028.99</v>
+        <v>2016.41</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3416.07</v>
+        <v>3394.89</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>986.59</v>
+        <v>980.47</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>3827.6</v>
+        <v>3803.87</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>808.14</v>
+        <v>803.13</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2845.22</v>
+        <v>2827.58</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>6081.03</v>
+        <v>6043.33</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2518.09</v>
+        <v>2502.48</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1089.51</v>
+        <v>1082.76</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>4540.9</v>
+        <v>4512.75</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>859.8099999999999</v>
+        <v>854.48</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1140.79</v>
+        <v>1133.72</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>891.64</v>
+        <v>886.11</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1596.67</v>
+        <v>1586.78</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>6164.82</v>
+        <v>6126.6</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1268.15</v>
+        <v>1260.29</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>5176.22</v>
+        <v>5144.13</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>8626</v>
+        <v>8572.52</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>9473.780000000001</v>
+        <v>9415.049999999999</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1210.3</v>
+        <v>1202.8</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>4203.75</v>
+        <v>4177.69</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2541.29</v>
+        <v>2525.53</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>3542.79</v>
+        <v>3520.83</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>4261.43</v>
+        <v>4235.01</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1058.86</v>
+        <v>1063.67</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>861.9400000000001</v>
+        <v>865.85</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1652.47</v>
+        <v>1659.97</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1193.18</v>
+        <v>1198.6</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>3442.24</v>
+        <v>3457.87</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1338.91</v>
+        <v>1344.99</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>16978.28</v>
+        <v>17055.39</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1796.49</v>
+        <v>1804.65</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1351.39</v>
+        <v>1357.52</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2942.48</v>
+        <v>2955.84</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2132.53</v>
+        <v>2142.21</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>793.61</v>
+        <v>797.22</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>796.98</v>
+        <v>800.6</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1851.27</v>
+        <v>1859.68</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>20435.42</v>
+        <v>20528.23</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>8700.889999999999</v>
+        <v>8740.41</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>792.8099999999999</v>
+        <v>796.41</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2379.25</v>
+        <v>2390.06</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>47922.24</v>
+        <v>48139.89</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>3577.9</v>
+        <v>3594.15</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1037.89</v>
+        <v>1042.6</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>1449.34</v>
+        <v>1455.92</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1649.88</v>
+        <v>1657.37</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2586.99</v>
+        <v>2598.74</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>804.92</v>
+        <v>808.5700000000001</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2940.8</v>
+        <v>2954.16</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1103.34</v>
+        <v>1108.36</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>35194.43</v>
+        <v>35718.49</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1119.36</v>
+        <v>1136.03</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>48738.95</v>
+        <v>49464.68</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>8001.35</v>
+        <v>8120.5</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1697.5</v>
+        <v>1722.77</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>6030.46</v>
+        <v>6120.25</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>830.62</v>
+        <v>842.99</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1515.37</v>
+        <v>1537.93</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1312.08</v>
+        <v>1331.61</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>10058.14</v>
+        <v>10207.91</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>845.87</v>
+        <v>858.47</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>1435.1</v>
+        <v>1456.47</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>8248.209999999999</v>
+        <v>8371.030000000001</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>3616.31</v>
+        <v>3670.16</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>827.28</v>
+        <v>839.6</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1094.21</v>
+        <v>1115.01</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1090.66</v>
+        <v>1111.39</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>796.39</v>
+        <v>811.53</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>5441.25</v>
+        <v>5544.7</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1562.75</v>
+        <v>1592.46</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1507.19</v>
+        <v>1535.84</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>59967.35</v>
+        <v>61107.42</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>2049.41</v>
+        <v>2088.37</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1888.49</v>
+        <v>1924.39</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>875.85</v>
+        <v>892.5</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>3244.43</v>
+        <v>3306.11</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>3895.87</v>
+        <v>3969.93</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2568.05</v>
+        <v>2616.87</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2302.72</v>
+        <v>2346.5</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1360.01</v>
+        <v>1385.87</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>857.9400000000001</v>
+        <v>874.25</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>953.83</v>
+        <v>971.97</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>4381.03</v>
+        <v>4464.32</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2007.88</v>
+        <v>2046.06</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>23806.18</v>
+        <v>24258.77</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>3273.92</v>
+        <v>3336.16</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>5696.76</v>
+        <v>5805.07</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1842.86</v>
+        <v>1877.89</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1282.21</v>
+        <v>1306.59</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>8749.299999999999</v>
+        <v>8915.639999999999</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2472.47</v>
+        <v>2519.48</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>4696.05</v>
+        <v>4785.33</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>966.22</v>
+        <v>984.59</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2120.8</v>
+        <v>2161.12</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>1773.83</v>
+        <v>1807.56</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1544.82</v>
+        <v>1574.19</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3676.4</v>
+        <v>3746.3</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>3473.64</v>
+        <v>3551.98</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>4079.16</v>
+        <v>4171.16</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>794.97</v>
+        <v>812.9</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>791.98</v>
+        <v>809.84</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>4954.12</v>
+        <v>5065.84</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>989.01</v>
+        <v>1011.31</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3278.71</v>
+        <v>3352.65</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2392.13</v>
+        <v>2446.08</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>1581.9</v>
+        <v>1617.58</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>4671.69</v>
+        <v>4777.05</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4053.15</v>
+        <v>4144.56</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2224.77</v>
+        <v>2274.94</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>792.5</v>
+        <v>810.37</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>1214.29</v>
+        <v>1241.68</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>794.45</v>
+        <v>812.37</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>2875.07</v>
+        <v>2939.91</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>6854.7</v>
+        <v>7009.29</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2228.34</v>
+        <v>2278.6</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>3067</v>
+        <v>3136.17</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>1692.98</v>
+        <v>1731.16</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1900.03</v>
+        <v>1942.88</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>814.88</v>
+        <v>833.25</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1440.49</v>
+        <v>1472.98</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>1206.69</v>
+        <v>1233.9</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1343.85</v>
+        <v>1374.15</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>1874.22</v>
+        <v>1916.49</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>985.3</v>
+        <v>1007.53</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>1106.94</v>
+        <v>1131.91</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1279.43</v>
+        <v>1308.28</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>795.34</v>
+        <v>813.27</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2120.72</v>
+        <v>2168.55</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>7518.54</v>
+        <v>7688.1</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>811.97</v>
+        <v>830.28</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2465.43</v>
+        <v>2521.04</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>1309.52</v>
+        <v>1339.06</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>3171.53</v>
+        <v>3243.06</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>1078.21</v>
+        <v>1102.53</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>14111.9</v>
+        <v>14430.16</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>1928.66</v>
+        <v>1972.16</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>1441.43</v>
+        <v>1473.93</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>3290.99</v>
+        <v>3365.21</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>867.08</v>
+        <v>886.63</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>980.84</v>
+        <v>1002.96</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>1927.45</v>
+        <v>1970.92</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2380.37</v>
+        <v>2434.06</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>6998.17</v>
+        <v>7156</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>829.88</v>
+        <v>848.6</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>2900.71</v>
+        <v>2966.13</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>3380.35</v>
+        <v>3456.58</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1156.52</v>
+        <v>1182.61</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1138.13</v>
+        <v>1163.79</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>1537.25</v>
+        <v>1547.87</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>844.9400000000001</v>
+        <v>850.77</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>10976.14</v>
+        <v>11051.92</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>4455.66</v>
+        <v>4486.42</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>3724.69</v>
+        <v>3750.41</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>2601.89</v>
+        <v>2619.86</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1058.66</v>
+        <v>1065.97</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>974.24</v>
+        <v>980.96</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>4979.84</v>
+        <v>5014.22</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>4938.78</v>
+        <v>4972.88</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1110.32</v>
+        <v>1117.99</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>2199.8</v>
+        <v>2214.98</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>13034.49</v>
+        <v>13124.48</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>2625.58</v>
+        <v>2643.71</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>1084.22</v>
+        <v>1091.7</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>4435.24</v>
+        <v>4465.87</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1645.07</v>
+        <v>1656.43</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>18241.15</v>
+        <v>18367.09</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>2209.88</v>
+        <v>2225.14</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>5517.4</v>
+        <v>5555.49</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>1131.27</v>
+        <v>1139.08</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>3097.48</v>
+        <v>3118.87</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>4917.38</v>
+        <v>4951.33</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>796.2</v>
+        <v>801.7</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>857.5</v>
+        <v>863.42</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>4055.65</v>
+        <v>4083.65</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>1118.68</v>
+        <v>1126.4</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>2631.9</v>
+        <v>2650.07</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>7139.6</v>
+        <v>7188.89</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>1235.62</v>
+        <v>1244.15</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>800.14</v>
+        <v>805.67</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>5320.2</v>
+        <v>5356.94</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>19983.43</v>
+        <v>20121.39</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1343.69</v>
+        <v>1352.97</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>2511.06</v>
+        <v>2528.4</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>812.0700000000001</v>
+        <v>817.67</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>1474.97</v>
+        <v>1485.16</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>3937.04</v>
+        <v>3964.22</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>1391.03</v>
+        <v>1395.33</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>896.83</v>
+        <v>899.61</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>1263.89</v>
+        <v>1267.8</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1737.02</v>
+        <v>1742.39</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>24427.43</v>
+        <v>24502.95</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1560.34</v>
+        <v>1565.17</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>30903.13</v>
+        <v>30998.67</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>4862.07</v>
+        <v>4877.1</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>1008.82</v>
+        <v>1011.94</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1372.44</v>
+        <v>1376.68</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>912.13</v>
+        <v>914.95</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1171.27</v>
+        <v>1174.89</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>1847.47</v>
+        <v>1853.18</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>2068.95</v>
+        <v>2075.34</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2508.08</v>
+        <v>2515.83</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>6934.08</v>
+        <v>6955.52</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>2536.4</v>
+        <v>2544.24</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1099.39</v>
+        <v>1102.79</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>913</v>
+        <v>915.8200000000001</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>1124.41</v>
+        <v>1127.88</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2561.18</v>
+        <v>2569.1</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>1294.24</v>
+        <v>1298.24</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>2106.86</v>
+        <v>2113.37</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>7089.24</v>
+        <v>7111.16</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2898.8</v>
+        <v>2907.76</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2252.06</v>
+        <v>2259.02</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>5461.79</v>
+        <v>5478.68</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>9158.309999999999</v>
+        <v>9186.629999999999</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>3835.83</v>
+        <v>3847.69</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>4047.86</v>
+        <v>4060.38</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>3026.1</v>
+        <v>3035.45</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>29823.49</v>
+        <v>29915.7</v>
       </c>
     </row>
     <row r="530">
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>1371.37</v>
+        <v>1375.61</v>
       </c>
     </row>
     <row r="531">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>1633.4</v>
+        <v>1638.45</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>919.24</v>
+        <v>922.08</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>2664.31</v>
+        <v>2672.54</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>7304.4</v>
+        <v>7326.98</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>808.8</v>
+        <v>811.3</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>816.01</v>
+        <v>818.53</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>3826.67</v>
+        <v>3838.5</v>
       </c>
     </row>
     <row r="538">
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>3228.43</v>
+        <v>3238.41</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1548.28</v>
+        <v>1553.07</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>1471.73</v>
+        <v>1467.84</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2526.39</v>
+        <v>2519.71</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2556.82</v>
+        <v>2550.05</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1252.39</v>
+        <v>1249.08</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>1375.33</v>
+        <v>1371.69</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>15167.75</v>
+        <v>15127.63</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>867.95</v>
+        <v>865.65</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>33233.24</v>
+        <v>33145.34</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1217.56</v>
+        <v>1214.34</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1036.53</v>
+        <v>1033.79</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>1099.39</v>
+        <v>1096.48</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>885.4400000000001</v>
+        <v>883.1</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>2524.91</v>
+        <v>2518.24</v>
       </c>
     </row>
     <row r="553">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>793.66</v>
+        <v>791.5599999999999</v>
       </c>
     </row>
     <row r="554">
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>3003.19</v>
+        <v>2995.25</v>
       </c>
     </row>
     <row r="555">
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>827.03</v>
+        <v>824.85</v>
       </c>
     </row>
     <row r="556">
@@ -34363,7 +34363,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>936.66</v>
+        <v>934.1799999999999</v>
       </c>
     </row>
     <row r="557">
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>6015.1</v>
+        <v>5999.19</v>
       </c>
     </row>
     <row r="558">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>3611.82</v>
+        <v>3602.27</v>
       </c>
     </row>
     <row r="559">
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>4657.11</v>
+        <v>4644.79</v>
       </c>
     </row>
     <row r="560">
@@ -34607,7 +34607,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>848.39</v>
+        <v>846.14</v>
       </c>
     </row>
     <row r="561">
@@ -34668,7 +34668,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1202.86</v>
+        <v>1199.68</v>
       </c>
     </row>
     <row r="562">
@@ -34729,7 +34729,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>1519.54</v>
+        <v>1515.52</v>
       </c>
     </row>
     <row r="563">
@@ -34790,7 +34790,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>4775.24</v>
+        <v>4762.61</v>
       </c>
     </row>
     <row r="564">
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>8486.559999999999</v>
+        <v>8464.120000000001</v>
       </c>
     </row>
     <row r="565">
@@ -34912,7 +34912,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1565.23</v>
+        <v>1561.09</v>
       </c>
     </row>
     <row r="566">
@@ -34973,7 +34973,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>2233.46</v>
+        <v>2227.55</v>
       </c>
     </row>
     <row r="567">
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>8330.41</v>
+        <v>8308.379999999999</v>
       </c>
     </row>
     <row r="568">
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>13071.81</v>
+        <v>13037.24</v>
       </c>
     </row>
     <row r="569">
@@ -35156,7 +35156,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>1116.83</v>
+        <v>1113.87</v>
       </c>
     </row>
     <row r="570">
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>22355.53</v>
+        <v>22296.4</v>
       </c>
     </row>
     <row r="571">
@@ -35278,7 +35278,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>10960.61</v>
+        <v>10931.62</v>
       </c>
     </row>
     <row r="572">
@@ -35339,7 +35339,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>13232.83</v>
+        <v>13197.83</v>
       </c>
     </row>
     <row r="573">
@@ -35400,7 +35400,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1750.45</v>
+        <v>1745.82</v>
       </c>
     </row>
     <row r="574">
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>1204.98</v>
+        <v>1201.79</v>
       </c>
     </row>
     <row r="575">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>2283.35</v>
+        <v>2252.94</v>
       </c>
     </row>
     <row r="576">
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>4116.71</v>
+        <v>4061.88</v>
       </c>
     </row>
     <row r="577">
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>1190.07</v>
+        <v>1174.22</v>
       </c>
     </row>
     <row r="578">
@@ -35705,7 +35705,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>4473.05</v>
+        <v>4413.47</v>
       </c>
     </row>
     <row r="579">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>1736.56</v>
+        <v>1713.42</v>
       </c>
     </row>
     <row r="580">
@@ -35827,7 +35827,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>922.38</v>
+        <v>910.09</v>
       </c>
     </row>
     <row r="581">
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>1000.89</v>
+        <v>987.5599999999999</v>
       </c>
     </row>
     <row r="582">
@@ -35949,7 +35949,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>5277.09</v>
+        <v>5206.8</v>
       </c>
     </row>
     <row r="583">
@@ -36010,7 +36010,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>1832.21</v>
+        <v>1807.81</v>
       </c>
     </row>
     <row r="584">
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>2043.58</v>
+        <v>2016.36</v>
       </c>
     </row>
     <row r="585">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>7194.92</v>
+        <v>7099.08</v>
       </c>
     </row>
     <row r="586">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>1919.79</v>
+        <v>1894.22</v>
       </c>
     </row>
     <row r="587">
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>1566.5</v>
+        <v>1545.63</v>
       </c>
     </row>
     <row r="588">
@@ -36315,7 +36315,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>6214.98</v>
+        <v>6132.2</v>
       </c>
     </row>
     <row r="589">
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>1880.75</v>
+        <v>1855.69</v>
       </c>
     </row>
     <row r="590">
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>8958.440000000001</v>
+        <v>8839.110000000001</v>
       </c>
     </row>
     <row r="591">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>1102.88</v>
+        <v>1088.19</v>
       </c>
     </row>
     <row r="592">
@@ -36559,7 +36559,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>16138.36</v>
+        <v>15923.39</v>
       </c>
     </row>
     <row r="593">
@@ -36620,7 +36620,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>801.87</v>
+        <v>791.1900000000001</v>
       </c>
     </row>
     <row r="594">
@@ -36681,7 +36681,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>1571.67</v>
+        <v>1550.73</v>
       </c>
     </row>
     <row r="595">
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>1237.65</v>
+        <v>1221.16</v>
       </c>
     </row>
     <row r="596">
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>4288.33</v>
+        <v>4231.21</v>
       </c>
     </row>
     <row r="597">
@@ -36864,7 +36864,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>2342.13</v>
+        <v>2310.93</v>
       </c>
     </row>
     <row r="598">
@@ -36925,7 +36925,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>5581.51</v>
+        <v>5507.17</v>
       </c>
     </row>
     <row r="599">
@@ -36986,7 +36986,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>4000.06</v>
+        <v>3946.78</v>
       </c>
     </row>
     <row r="600">
@@ -37047,7 +37047,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>841.79</v>
+        <v>830.58</v>
       </c>
     </row>
     <row r="601">
@@ -37108,7 +37108,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>23464.05</v>
+        <v>23151.5</v>
       </c>
     </row>
     <row r="602">
@@ -37169,7 +37169,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>3521</v>
+        <v>3474.1</v>
       </c>
     </row>
     <row r="603">
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1038.86</v>
+        <v>1025.03</v>
       </c>
     </row>
     <row r="604">
@@ -37291,7 +37291,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>10954.41</v>
+        <v>10808.49</v>
       </c>
     </row>
     <row r="605">
@@ -37352,7 +37352,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>3213.92</v>
+        <v>3171.11</v>
       </c>
     </row>
     <row r="606">
@@ -37413,7 +37413,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>916.95</v>
+        <v>904.74</v>
       </c>
     </row>
     <row r="607">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1227.54</v>
+        <v>1211.19</v>
       </c>
     </row>
     <row r="608">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>2075.83</v>
+        <v>2048.18</v>
       </c>
     </row>
     <row r="609">
@@ -37596,7 +37596,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>794.14</v>
+        <v>783.5700000000001</v>
       </c>
     </row>
     <row r="610">
@@ -37657,7 +37657,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>10057.4</v>
+        <v>9923.43</v>
       </c>
     </row>
     <row r="611">
@@ -37718,7 +37718,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>4511.33</v>
+        <v>4451.24</v>
       </c>
     </row>
     <row r="612">
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>8708.76</v>
+        <v>8592.76</v>
       </c>
     </row>
     <row r="613">
@@ -37840,7 +37840,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>1370.54</v>
+        <v>1352.28</v>
       </c>
     </row>
     <row r="614">
@@ -37901,7 +37901,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>6363.38</v>
+        <v>6278.61</v>
       </c>
     </row>
     <row r="615">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>1777.89</v>
+        <v>1754.21</v>
       </c>
     </row>
     <row r="616">
@@ -38023,7 +38023,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>888.59</v>
+        <v>876.76</v>
       </c>
     </row>
     <row r="617">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>1418.98</v>
+        <v>1400.07</v>
       </c>
     </row>
     <row r="618">
@@ -38145,7 +38145,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>1527.72</v>
+        <v>1507.38</v>
       </c>
     </row>
     <row r="619">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>8342.790000000001</v>
+        <v>8179.49</v>
       </c>
     </row>
     <row r="620">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>2330.97</v>
+        <v>2285.35</v>
       </c>
     </row>
     <row r="621">
@@ -38328,7 +38328,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>17630.8</v>
+        <v>17285.69</v>
       </c>
     </row>
     <row r="622">
@@ -38389,7 +38389,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>977.0599999999999</v>
+        <v>957.9299999999999</v>
       </c>
     </row>
     <row r="623">
@@ -38450,7 +38450,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>1967.48</v>
+        <v>1928.96</v>
       </c>
     </row>
     <row r="624">
@@ -38511,7 +38511,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1056.32</v>
+        <v>1035.64</v>
       </c>
     </row>
     <row r="625">
@@ -38572,7 +38572,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>7747.93</v>
+        <v>7596.27</v>
       </c>
     </row>
     <row r="626">
@@ -38633,7 +38633,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>3768.05</v>
+        <v>3694.29</v>
       </c>
     </row>
     <row r="627">
@@ -38694,7 +38694,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>4936.5</v>
+        <v>4839.88</v>
       </c>
     </row>
     <row r="628">
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>980.79</v>
+        <v>961.6</v>
       </c>
     </row>
     <row r="629">
@@ -38816,7 +38816,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>1837.31</v>
+        <v>1801.34</v>
       </c>
     </row>
     <row r="630">
@@ -38877,7 +38877,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>2463.95</v>
+        <v>2415.72</v>
       </c>
     </row>
     <row r="631">
@@ -38938,7 +38938,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>2033.6</v>
+        <v>1993.79</v>
       </c>
     </row>
     <row r="632">
@@ -38999,7 +38999,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>2585.52</v>
+        <v>2534.91</v>
       </c>
     </row>
     <row r="633">
@@ -39060,7 +39060,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>2016.4</v>
+        <v>1976.93</v>
       </c>
     </row>
     <row r="634">
@@ -39121,7 +39121,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2058.33</v>
+        <v>2018.04</v>
       </c>
     </row>
     <row r="635">
@@ -39182,7 +39182,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>10217.16</v>
+        <v>10017.17</v>
       </c>
     </row>
     <row r="636">
@@ -39243,7 +39243,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>3295.19</v>
+        <v>3230.69</v>
       </c>
     </row>
     <row r="637">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1138.13</v>
+        <v>1115.85</v>
       </c>
     </row>
     <row r="638">
@@ -39365,7 +39365,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>2221.9</v>
+        <v>2178.41</v>
       </c>
     </row>
     <row r="639">
@@ -39426,7 +39426,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>2523.27</v>
+        <v>2473.88</v>
       </c>
     </row>
     <row r="640">
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>1285.35</v>
+        <v>1260.19</v>
       </c>
     </row>
     <row r="641">
@@ -39548,7 +39548,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>1172.83</v>
+        <v>1149.87</v>
       </c>
     </row>
     <row r="642">
@@ -39609,7 +39609,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>1028.36</v>
+        <v>1008.24</v>
       </c>
     </row>
     <row r="643">
@@ -39670,7 +39670,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>807.09</v>
+        <v>791.29</v>
       </c>
     </row>
     <row r="644">
@@ -39731,7 +39731,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>2105</v>
+        <v>2063.79</v>
       </c>
     </row>
     <row r="645">
@@ -39792,7 +39792,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>38878.96</v>
+        <v>38117.95</v>
       </c>
     </row>
     <row r="646">
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>28508.24</v>
+        <v>27950.22</v>
       </c>
     </row>
     <row r="647">
@@ -39914,7 +39914,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>1242.22</v>
+        <v>1217.91</v>
       </c>
     </row>
     <row r="648">
@@ -39975,7 +39975,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>3183.28</v>
+        <v>3120.97</v>
       </c>
     </row>
     <row r="649">
@@ -40036,7 +40036,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>1615.78</v>
+        <v>1584.15</v>
       </c>
     </row>
     <row r="650">
@@ -40097,7 +40097,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>4324.2</v>
+        <v>4239.56</v>
       </c>
     </row>
     <row r="651">
@@ -40158,7 +40158,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>896.42</v>
+        <v>878.87</v>
       </c>
     </row>
     <row r="652">
@@ -40219,7 +40219,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>841.85</v>
+        <v>825.38</v>
       </c>
     </row>
     <row r="653">
@@ -40280,7 +40280,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>836.05</v>
+        <v>819.6799999999999</v>
       </c>
     </row>
     <row r="654">
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>973.9299999999999</v>
+        <v>954.86</v>
       </c>
     </row>
     <row r="655">
@@ -40402,7 +40402,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>839.17</v>
+        <v>822.74</v>
       </c>
     </row>
     <row r="656">
@@ -40463,7 +40463,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>1847.57</v>
+        <v>1811.41</v>
       </c>
     </row>
     <row r="657">
@@ -40524,7 +40524,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>3539.66</v>
+        <v>3470.38</v>
       </c>
     </row>
     <row r="658">
@@ -40585,7 +40585,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>1145.78</v>
+        <v>1123.35</v>
       </c>
     </row>
     <row r="659">
@@ -40646,7 +40646,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>1611.06</v>
+        <v>1579.52</v>
       </c>
     </row>
     <row r="660">
@@ -40707,7 +40707,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>3392.64</v>
+        <v>3342.38</v>
       </c>
     </row>
     <row r="661">
@@ -40768,7 +40768,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>2197.69</v>
+        <v>2165.13</v>
       </c>
     </row>
     <row r="662">
@@ -40829,7 +40829,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>3884.61</v>
+        <v>3827.05</v>
       </c>
     </row>
     <row r="663">
@@ -40890,7 +40890,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>1374.32</v>
+        <v>1353.96</v>
       </c>
     </row>
     <row r="664">
@@ -40951,7 +40951,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>5690.09</v>
+        <v>5605.79</v>
       </c>
     </row>
     <row r="665">
@@ -41012,7 +41012,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>5982.96</v>
+        <v>5894.31</v>
       </c>
     </row>
     <row r="666">
@@ -41073,7 +41073,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>1378.02</v>
+        <v>1357.6</v>
       </c>
     </row>
     <row r="667">
@@ -41134,7 +41134,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>857.45</v>
+        <v>844.75</v>
       </c>
     </row>
     <row r="668">
@@ -41195,7 +41195,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>4518.71</v>
+        <v>4451.76</v>
       </c>
     </row>
     <row r="669">
@@ -41256,7 +41256,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>1997.89</v>
+        <v>1968.29</v>
       </c>
     </row>
     <row r="670">
@@ -41317,7 +41317,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>1746.54</v>
+        <v>1720.66</v>
       </c>
     </row>
     <row r="671">
@@ -41378,7 +41378,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>2866.11</v>
+        <v>2823.65</v>
       </c>
     </row>
     <row r="672">
@@ -41439,7 +41439,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>4445.72</v>
+        <v>4379.85</v>
       </c>
     </row>
     <row r="673">
@@ -41500,7 +41500,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>3617.54</v>
+        <v>3563.94</v>
       </c>
     </row>
     <row r="674">
@@ -41561,7 +41561,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>14068.77</v>
+        <v>13860.33</v>
       </c>
     </row>
     <row r="675">
@@ -41622,7 +41622,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>1576.34</v>
+        <v>1552.99</v>
       </c>
     </row>
     <row r="676">
@@ -41683,7 +41683,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2557.81</v>
+        <v>2519.92</v>
       </c>
     </row>
     <row r="677">
@@ -41744,7 +41744,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>2539.7</v>
+        <v>2502.07</v>
       </c>
     </row>
     <row r="678">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>5277.09</v>
+        <v>5198.91</v>
       </c>
     </row>
     <row r="679">
@@ -41866,7 +41866,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>1611.86</v>
+        <v>1587.98</v>
       </c>
     </row>
     <row r="680">
@@ -41927,7 +41927,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>2807.29</v>
+        <v>2765.7</v>
       </c>
     </row>
     <row r="681">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>1178.06</v>
+        <v>1160.61</v>
       </c>
     </row>
     <row r="682">
@@ -42049,7 +42049,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>797.72</v>
+        <v>785.9</v>
       </c>
     </row>
     <row r="683">
@@ -42110,7 +42110,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>4498.93</v>
+        <v>4432.28</v>
       </c>
     </row>
     <row r="684">
@@ -42171,7 +42171,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>1573.28</v>
+        <v>1549.97</v>
       </c>
     </row>
     <row r="685">
@@ -42232,7 +42232,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>1338.55</v>
+        <v>1318.72</v>
       </c>
     </row>
     <row r="686">
@@ -42293,7 +42293,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>5021.75</v>
+        <v>4947.34</v>
       </c>
     </row>
     <row r="687">
@@ -42354,7 +42354,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1865.31</v>
+        <v>1837.67</v>
       </c>
     </row>
     <row r="688">
@@ -42415,7 +42415,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>1995.39</v>
+        <v>1965.83</v>
       </c>
     </row>
     <row r="689">
@@ -42476,7 +42476,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>2755.73</v>
+        <v>2714.9</v>
       </c>
     </row>
     <row r="690">
@@ -42537,7 +42537,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>1380.54</v>
+        <v>1360.08</v>
       </c>
     </row>
     <row r="691">
@@ -42598,7 +42598,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>2994.38</v>
+        <v>2950.02</v>
       </c>
     </row>
     <row r="692">
@@ -42659,7 +42659,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>3637.89</v>
+        <v>3583.99</v>
       </c>
     </row>
     <row r="693">
@@ -42720,7 +42720,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>3319.43</v>
+        <v>3270.25</v>
       </c>
     </row>
     <row r="694">
@@ -42781,7 +42781,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>1097.48</v>
+        <v>1081.22</v>
       </c>
     </row>
     <row r="695">
@@ -42842,7 +42842,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>21688.17</v>
+        <v>21366.84</v>
       </c>
     </row>
     <row r="696">
@@ -42903,7 +42903,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>1246.03</v>
+        <v>1227.57</v>
       </c>
     </row>
     <row r="697">
@@ -42964,7 +42964,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>800.1</v>
+        <v>783.66</v>
       </c>
     </row>
     <row r="698">
@@ -43025,7 +43025,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>10019.67</v>
+        <v>9813.75</v>
       </c>
     </row>
     <row r="699">
@@ -43086,7 +43086,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>2519.49</v>
+        <v>2467.71</v>
       </c>
     </row>
     <row r="700">
@@ -43147,7 +43147,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>829.84</v>
+        <v>812.79</v>
       </c>
     </row>
     <row r="701">
@@ -43208,7 +43208,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>1183.28</v>
+        <v>1158.96</v>
       </c>
     </row>
     <row r="702">
@@ -43269,7 +43269,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>16553.29</v>
+        <v>16213.1</v>
       </c>
     </row>
     <row r="703">
@@ -43330,7 +43330,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>3592.59</v>
+        <v>3518.75</v>
       </c>
     </row>
     <row r="704">
@@ -43391,7 +43391,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>6252.58</v>
+        <v>6124.08</v>
       </c>
     </row>
     <row r="705">
@@ -43452,7 +43452,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>6876.14</v>
+        <v>6734.83</v>
       </c>
     </row>
     <row r="706">
@@ -43513,7 +43513,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2525.47</v>
+        <v>2473.57</v>
       </c>
     </row>
     <row r="707">
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>1335.92</v>
+        <v>1308.47</v>
       </c>
     </row>
     <row r="708">
@@ -43635,7 +43635,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>22901.03</v>
+        <v>22430.37</v>
       </c>
     </row>
     <row r="709">
@@ -43696,7 +43696,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>981.04</v>
+        <v>960.87</v>
       </c>
     </row>
     <row r="710">
@@ -43757,7 +43757,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>2590.82</v>
+        <v>2537.57</v>
       </c>
     </row>
     <row r="711">
@@ -43818,7 +43818,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>1152.19</v>
+        <v>1128.51</v>
       </c>
     </row>
     <row r="712">
@@ -43879,7 +43879,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>24394.61</v>
+        <v>23893.26</v>
       </c>
     </row>
     <row r="713">
@@ -43940,7 +43940,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1718.11</v>
+        <v>1682.8</v>
       </c>
     </row>
     <row r="714">
@@ -44001,7 +44001,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>7284.58</v>
+        <v>7134.87</v>
       </c>
     </row>
     <row r="715">
@@ -44062,7 +44062,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>9061.809999999999</v>
+        <v>8875.57</v>
       </c>
     </row>
     <row r="716">
@@ -44123,7 +44123,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>3691.82</v>
+        <v>3615.94</v>
       </c>
     </row>
     <row r="717">
@@ -44184,7 +44184,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>3293.17</v>
+        <v>3225.49</v>
       </c>
     </row>
     <row r="718">
@@ -44245,7 +44245,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>4609.78</v>
+        <v>4515.04</v>
       </c>
     </row>
     <row r="719">
@@ -44306,7 +44306,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>976.99</v>
+        <v>956.91</v>
       </c>
     </row>
     <row r="720">
@@ -44367,7 +44367,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>1424.28</v>
+        <v>1395.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jun-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38064,7 +38064,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -40382,7 +40382,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40687,7 +40687,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40992,7 +40992,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41602,7 +41602,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41663,7 +41663,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41724,7 +41724,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41968,7 +41968,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42151,7 +42151,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -43310,7 +43310,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43493,7 +43493,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43920,7 +43920,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -44286,7 +44286,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jun-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jun-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1777,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2094,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2411,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2476,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2541,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2728,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2793,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2858,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2988,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3114,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3305,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3431,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3496,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3561,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3626,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3691,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3756,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3821,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3951,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4016,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4264,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4390,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4455,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4520,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4650,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4776,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4841,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4906,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4971,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5036,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5101,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5166,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5231,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5296,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5361,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5426,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5491,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5556,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5621,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5747,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5812,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5877,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5942,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6068,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6194,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6320,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6385,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6450,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6515,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6580,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6706,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6832,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6958,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7023,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7088,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7153,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7218,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7344,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7470,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7535,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7600,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7665,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7730,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7856,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7921,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7986,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8051,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8116,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8181,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8246,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8311,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8376,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8441,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8506,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8571,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8636,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8762,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8827,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8953,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9018,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9083,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9148,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9278,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9343,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9408,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9534,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9599,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9664,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9729,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9794,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9859,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9924,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10050,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10115,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10180,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10245,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10310,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10375,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10440,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10505,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10631,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10696,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10761,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10826,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10891,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10956,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11021,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11086,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11151,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11216,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11281,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11407,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11472,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11537,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11602,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11667,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11732,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11797,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11862,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11992,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12057,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12122,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12187,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12252,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12317,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12382,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12447,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12573,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12638,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12703,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12890,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12955,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13020,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13085,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13150,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13215,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13280,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13345,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13410,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13475,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13540,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13605,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13670,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13735,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13800,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13865,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13930,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14056,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14121,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14186,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14251,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14316,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14442,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14507,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14572,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14637,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14702,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14767,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14954,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15019,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15084,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15149,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15214,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15340,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15405,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15470,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15535,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15600,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15726,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15978,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16043,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16108,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16234,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16299,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16364,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16429,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16555,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16681,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16746,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16872,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16937,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17124,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17189,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17315,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17380,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17445,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17510,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17575,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17640,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17705,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17770,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17835,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17900,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17965,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18091,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18156,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18221,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18286,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18351,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18599,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18664,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18912,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19042,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19172,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19237,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19302,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19367,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19432,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19558,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19623,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19688,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19883,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19948,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20013,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20078,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20143,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20208,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20273,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20338,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20403,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20468,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20533,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20598,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20724,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20789,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20854,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20919,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20984,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21049,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21175,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21301,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21366,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21431,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21496,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21561,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21626,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21817,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21882,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22012,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22268,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22333,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22398,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22463,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22589,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22654,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22784,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22849,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22914,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22979,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23044,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23109,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23174,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23422,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23487,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23552,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23617,11 @@
           <t>77.743.075-0</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23682,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23747,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23877,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23942,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24007,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24133,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24198,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24263,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24328,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24393,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24458,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24649,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24714,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24779,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24844,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25031,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25096,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25222,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25287,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25352,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25417,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25482,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25547,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25673,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25738,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25803,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25868,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25933,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25998,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26063,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26128,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26193,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26258,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26323,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26388,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26453,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26518,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26583,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26648,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26713,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26778,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26843,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26973,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27038,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27103,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27290,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27355,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27420,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27485,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27550,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27615,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27680,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27867,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27932,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27997,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28123,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28188,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28375,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28440,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28505,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28570,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28696,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28761,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28826,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29017,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29082,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29208,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29273,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29338,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29403,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29468,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29533,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29659,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29724,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29854,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29919,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29984,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30049,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30114,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30244,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30309,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30374,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30439,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30504,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30569,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30634,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30699,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30764,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30829,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30894,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30959,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31085,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31150,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31215,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31406,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31532,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31597,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31662,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31727,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31792,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31857,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31922,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31987,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +32052,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32117,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32308,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32438,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32629,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32755,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32820,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32885,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32950,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +33015,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +33080,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +33145,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33332,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33397,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33462,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33527,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33592,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33657,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33722,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33787,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33852,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33917,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33982,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +34047,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +34112,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34177,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34242,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34307,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34372,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34437,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34502,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34567,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34632,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34697,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +34762,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34888,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34953,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +35018,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +35144,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35209,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35274,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35339,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35404,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35469,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35534,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35599,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35664,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35729,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35794,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35859,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35924,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35989,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +36054,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +36119,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +36184,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +36249,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +36314,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36379,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +36444,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36509,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36635,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +36887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36952,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +37017,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +37082,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +37147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35332,7 +37212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +37277,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +37342,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +37407,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37472,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37537,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37602,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +37667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +37732,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37797,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +37862,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +37927,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37992,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +38057,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +38122,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +38248,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +38313,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38439,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +38504,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38630,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38695,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +38760,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38890,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38955,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +39020,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +39085,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +39150,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +39215,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +39280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +39345,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +39410,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +39475,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39540,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39605,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39670,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39735,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39800,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39865,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39930,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +39995,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +40243,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38260,7 +40308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +40373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +40438,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +40625,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +40690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +40816,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +40942,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +41007,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +41072,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +41137,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +41202,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39175,7 +41267,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39236,7 +41332,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +41397,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +41462,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +41527,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +41592,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +41657,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +41722,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +41787,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +41852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +41917,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +41982,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +42047,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +42112,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +42177,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +42242,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40151,7 +42307,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +42372,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40273,7 +42437,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +42502,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +42567,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40456,7 +42632,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +42697,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +42762,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40639,7 +42827,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40761,7 +42953,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40822,7 +43018,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +43083,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +43148,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +43213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41066,7 +43278,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +43343,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41188,7 +43408,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41310,7 +43534,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41371,7 +43599,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41432,7 +43664,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41493,7 +43729,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41554,7 +43794,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41615,7 +43859,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41676,7 +43924,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41737,7 +43989,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41798,7 +44054,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41859,7 +44119,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41920,7 +44184,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42103,7 +44371,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42164,7 +44436,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42225,7 +44501,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42286,7 +44566,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42408,7 +44692,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42469,7 +44757,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42530,7 +44822,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42591,7 +44887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42652,7 +44952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42713,7 +45017,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42774,7 +45082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42835,7 +45147,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42896,7 +45212,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42957,7 +45277,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43079,7 +45403,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43140,7 +45468,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43262,7 +45594,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43384,7 +45720,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43445,7 +45785,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43506,7 +45850,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43567,7 +45915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43628,7 +45980,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43689,7 +46045,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43811,7 +46171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43872,7 +46236,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43933,7 +46301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43994,7 +46366,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44055,7 +46431,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44116,7 +46496,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44238,7 +46622,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44299,7 +46687,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44360,7 +46752,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44421,7 +46817,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44482,7 +46882,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44543,7 +46947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44604,7 +47012,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
